--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_aysen.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:47</t>
+    <t xml:space="preserve">2026-09-09 20:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_aysen.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:09</t>
+    <t xml:space="preserve">2026-09-18 17:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_aysen.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_aysen.xlsx
@@ -30,36 +30,36 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Río Ibáñez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile Chico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cochrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aysén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coyhaique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guaitecas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tortel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lago Verde</t>
+  </si>
+  <si>
     <t xml:space="preserve">O'Higgins</t>
   </si>
   <si>
-    <t xml:space="preserve">Lago Verde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tortel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guaitecas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cochrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chile Chico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Ibáñez</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:05</t>
+    <t xml:space="preserve">2026-09-27 21:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -489,13 +489,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>475</v>
+        <v>3178</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>670</v>
+        <v>2708</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>70.9</v>
+        <v>117.36</v>
       </c>
     </row>
     <row r="3">
@@ -503,13 +503,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>832</v>
+        <v>5869</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>917</v>
+        <v>5148</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>90.73</v>
+        <v>114.01</v>
       </c>
     </row>
     <row r="4">
@@ -517,13 +517,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>547</v>
+        <v>4189</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>579</v>
+        <v>3718</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>94.47</v>
+        <v>112.67</v>
       </c>
     </row>
     <row r="5">
@@ -531,13 +531,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1559</v>
+        <v>28217</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1607</v>
+        <v>25138</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>97.01</v>
+        <v>112.25</v>
       </c>
     </row>
     <row r="6">
@@ -545,13 +545,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5948</v>
+        <v>64800</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5857</v>
+        <v>61705</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>101.55</v>
+        <v>105.02</v>
       </c>
     </row>
     <row r="7">
@@ -559,13 +559,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>64800</v>
+        <v>5948</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>61705</v>
+        <v>5857</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>105.02</v>
+        <v>101.55</v>
       </c>
     </row>
     <row r="8">
@@ -573,13 +573,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>28217</v>
+        <v>1559</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>25138</v>
+        <v>1607</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>112.25</v>
+        <v>97.01</v>
       </c>
     </row>
     <row r="9">
@@ -587,13 +587,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4189</v>
+        <v>547</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3718</v>
+        <v>579</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>112.67</v>
+        <v>94.47</v>
       </c>
     </row>
     <row r="10">
@@ -601,13 +601,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5869</v>
+        <v>832</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5148</v>
+        <v>917</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>114.01</v>
+        <v>90.73</v>
       </c>
     </row>
     <row r="11">
@@ -615,13 +615,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3178</v>
+        <v>475</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2708</v>
+        <v>670</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>117.36</v>
+        <v>70.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_aysen.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:51</t>
+    <t xml:space="preserve">2026-10-05 05:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
